--- a/pseudodata/2001.xlsx
+++ b/pseudodata/2001.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P22"/>
+  <dimension ref="A1:O35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,60 +451,55 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Zmin</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Zmax</t>
+          <t>T</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>Z</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>obs</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>obs</t>
+          <t>lum</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>lum</t>
+          <t>value</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>value</t>
+          <t>stat_u</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>stat_u</t>
+          <t>sys_u</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>sys_u</t>
+          <t>tar</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>tar</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>norm_c</t>
         </is>
@@ -524,43 +519,40 @@
         <v>100</v>
       </c>
       <c r="E2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G2" t="n">
         <v>0.2</v>
       </c>
-      <c r="F2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G2" t="n">
-        <v>2</v>
-      </c>
       <c r="H2" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I2" t="n">
-        <v>50</v>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>cos(phi_Dp)</t>
-        </is>
+        <v>40</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>10</v>
       </c>
       <c r="K2" t="n">
-        <v>10</v>
+        <v>-0.001725446200197124</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.003079333255803665</v>
+        <v>0.000666462883381535</v>
       </c>
       <c r="M2" t="n">
-        <v>0.000530860538661124</v>
-      </c>
-      <c r="N2" t="n">
-        <v>-0.0001539666627901833</v>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>d</t>
-        </is>
-      </c>
-      <c r="P2" t="n">
+        <v>-8.627231000985621e-05</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>p</t>
+        </is>
+      </c>
+      <c r="O2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -578,43 +570,40 @@
         <v>100</v>
       </c>
       <c r="E3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G3" t="n">
         <v>0.2</v>
       </c>
-      <c r="F3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G3" t="n">
-        <v>2.5</v>
-      </c>
       <c r="H3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I3" t="n">
-        <v>50</v>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>cos(phi_Dp)</t>
-        </is>
+        <v>40</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>10</v>
       </c>
       <c r="K3" t="n">
-        <v>10</v>
+        <v>-0.002217030975399952</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.003006949307339891</v>
+        <v>0.0006570404224291923</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0007155908433810673</v>
-      </c>
-      <c r="N3" t="n">
-        <v>-0.0001503474653669945</v>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>d</t>
-        </is>
-      </c>
-      <c r="P3" t="n">
+        <v>-0.0001108515487699976</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>p</t>
+        </is>
+      </c>
+      <c r="O3" t="n">
         <v>1</v>
       </c>
     </row>
@@ -632,43 +621,40 @@
         <v>100</v>
       </c>
       <c r="E4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G4" t="n">
         <v>0.2</v>
       </c>
-      <c r="F4" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G4" t="n">
-        <v>3</v>
-      </c>
       <c r="H4" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I4" t="n">
-        <v>50</v>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>cos(phi_Dp)</t>
-        </is>
+        <v>40</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>10</v>
       </c>
       <c r="K4" t="n">
-        <v>10</v>
+        <v>-0.002811772519484476</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.002043946354555173</v>
+        <v>0.0007080521697189179</v>
       </c>
       <c r="M4" t="n">
-        <v>0.001008716826647291</v>
-      </c>
-      <c r="N4" t="n">
-        <v>-0.0001021973177277587</v>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>d</t>
-        </is>
-      </c>
-      <c r="P4" t="n">
+        <v>-0.0001405886259742238</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>p</t>
+        </is>
+      </c>
+      <c r="O4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -686,43 +672,40 @@
         <v>100</v>
       </c>
       <c r="E5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G5" t="n">
         <v>0.2</v>
       </c>
-      <c r="F5" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G5" t="n">
-        <v>3.5</v>
-      </c>
       <c r="H5" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I5" t="n">
-        <v>50</v>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>cos(phi_Dp)</t>
-        </is>
+        <v>40</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>10</v>
       </c>
       <c r="K5" t="n">
-        <v>10</v>
+        <v>-0.003592630914524652</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.0004607113480824245</v>
+        <v>0.0008221728083093548</v>
       </c>
       <c r="M5" t="n">
-        <v>0.001437876241392241</v>
-      </c>
-      <c r="N5" t="n">
-        <v>-2.303556740412122e-05</v>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>d</t>
-        </is>
-      </c>
-      <c r="P5" t="n">
+        <v>-0.0001796315457262326</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>p</t>
+        </is>
+      </c>
+      <c r="O5" t="n">
         <v>1</v>
       </c>
     </row>
@@ -740,43 +723,40 @@
         <v>100</v>
       </c>
       <c r="E6" t="n">
+        <v>4</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G6" t="n">
         <v>0.2</v>
       </c>
-      <c r="F6" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G6" t="n">
-        <v>4</v>
-      </c>
       <c r="H6" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I6" t="n">
-        <v>50</v>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>cos(phi_Dp)</t>
-        </is>
+        <v>40</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>10</v>
       </c>
       <c r="K6" t="n">
-        <v>10</v>
+        <v>-0.004651829946727361</v>
       </c>
       <c r="L6" t="n">
-        <v>0.001543065669891697</v>
+        <v>0.001013387598759933</v>
       </c>
       <c r="M6" t="n">
-        <v>0.002048265683601953</v>
-      </c>
-      <c r="N6" t="n">
-        <v>7.715328349458487e-05</v>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>d</t>
-        </is>
-      </c>
-      <c r="P6" t="n">
+        <v>-0.0002325914973363681</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>p</t>
+        </is>
+      </c>
+      <c r="O6" t="n">
         <v>1</v>
       </c>
     </row>
@@ -794,43 +774,40 @@
         <v>100</v>
       </c>
       <c r="E7" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G7" t="n">
         <v>0.2</v>
       </c>
-      <c r="F7" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G7" t="n">
-        <v>4.5</v>
-      </c>
       <c r="H7" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I7" t="n">
-        <v>50</v>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>cos(phi_Dp)</t>
-        </is>
+        <v>40</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>10</v>
       </c>
       <c r="K7" t="n">
-        <v>10</v>
+        <v>-0.006089718257006102</v>
       </c>
       <c r="L7" t="n">
-        <v>0.003810855295206269</v>
+        <v>0.001305146732588562</v>
       </c>
       <c r="M7" t="n">
-        <v>0.002840458150573266</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0.0001905427647603135</v>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>d</t>
-        </is>
-      </c>
-      <c r="P7" t="n">
+        <v>-0.0003044859128503051</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>p</t>
+        </is>
+      </c>
+      <c r="O7" t="n">
         <v>1</v>
       </c>
     </row>
@@ -848,43 +825,40 @@
         <v>100</v>
       </c>
       <c r="E8" t="n">
+        <v>5</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G8" t="n">
         <v>0.2</v>
       </c>
-      <c r="F8" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G8" t="n">
-        <v>5</v>
-      </c>
       <c r="H8" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I8" t="n">
-        <v>50</v>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>cos(phi_Dp)</t>
-        </is>
+        <v>40</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>10</v>
       </c>
       <c r="K8" t="n">
-        <v>10</v>
+        <v>-0.008008788324369931</v>
       </c>
       <c r="L8" t="n">
-        <v>0.006005226104739806</v>
+        <v>0.001729528303021897</v>
       </c>
       <c r="M8" t="n">
-        <v>0.003745373962914396</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0.0003002613052369903</v>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>d</t>
-        </is>
-      </c>
-      <c r="P8" t="n">
+        <v>-0.0004004394162184966</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>p</t>
+        </is>
+      </c>
+      <c r="O8" t="n">
         <v>1</v>
       </c>
     </row>
@@ -902,43 +876,40 @@
         <v>100</v>
       </c>
       <c r="E9" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G9" t="n">
         <v>0.2</v>
       </c>
-      <c r="F9" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G9" t="n">
-        <v>2</v>
-      </c>
       <c r="H9" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I9" t="n">
-        <v>50</v>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>cos(phi_Dp)cos(phi_kp)</t>
-        </is>
+        <v>40</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>10</v>
       </c>
       <c r="K9" t="n">
-        <v>10</v>
+        <v>-0.01051076022486574</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.0009429285995471301</v>
+        <v>0.002327386315095466</v>
       </c>
       <c r="M9" t="n">
-        <v>0.000530860538661124</v>
-      </c>
-      <c r="N9" t="n">
-        <v>-4.714642997735651e-05</v>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>d</t>
-        </is>
-      </c>
-      <c r="P9" t="n">
+        <v>-0.000525538011243287</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>p</t>
+        </is>
+      </c>
+      <c r="O9" t="n">
         <v>1</v>
       </c>
     </row>
@@ -956,43 +927,40 @@
         <v>100</v>
       </c>
       <c r="E10" t="n">
+        <v>6</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G10" t="n">
         <v>0.2</v>
       </c>
-      <c r="F10" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G10" t="n">
-        <v>2.5</v>
-      </c>
       <c r="H10" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I10" t="n">
-        <v>50</v>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>cos(phi_Dp)cos(phi_kp)</t>
-        </is>
+        <v>40</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>10</v>
       </c>
       <c r="K10" t="n">
-        <v>10</v>
+        <v>-0.013702122144424</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.001444926920518763</v>
+        <v>0.00314850804831056</v>
       </c>
       <c r="M10" t="n">
-        <v>0.0007155908433810673</v>
-      </c>
-      <c r="N10" t="n">
-        <v>-7.224634602593813e-05</v>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>d</t>
-        </is>
-      </c>
-      <c r="P10" t="n">
+        <v>-0.0006851061072212002</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>p</t>
+        </is>
+      </c>
+      <c r="O10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1010,43 +978,40 @@
         <v>100</v>
       </c>
       <c r="E11" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G11" t="n">
         <v>0.2</v>
       </c>
-      <c r="F11" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G11" t="n">
-        <v>3</v>
-      </c>
       <c r="H11" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I11" t="n">
-        <v>50</v>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>cos(phi_Dp)cos(phi_kp)</t>
-        </is>
+        <v>40</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>10</v>
       </c>
       <c r="K11" t="n">
-        <v>10</v>
+        <v>-0.01768739928708588</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.00151732373802449</v>
+        <v>0.004244103034057005</v>
       </c>
       <c r="M11" t="n">
-        <v>0.001008716826647291</v>
-      </c>
-      <c r="N11" t="n">
-        <v>-7.586618690122449e-05</v>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>d</t>
-        </is>
-      </c>
-      <c r="P11" t="n">
+        <v>-0.0008843699643542942</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>p</t>
+        </is>
+      </c>
+      <c r="O11" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1064,43 +1029,40 @@
         <v>100</v>
       </c>
       <c r="E12" t="n">
+        <v>7</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G12" t="n">
         <v>0.2</v>
       </c>
-      <c r="F12" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G12" t="n">
-        <v>3.5</v>
-      </c>
       <c r="H12" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I12" t="n">
-        <v>50</v>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>cos(phi_Dp)cos(phi_kp)</t>
-        </is>
+        <v>40</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>10</v>
       </c>
       <c r="K12" t="n">
-        <v>10</v>
+        <v>-0.02249478803256518</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.001170100082762613</v>
+        <v>0.005638921215013686</v>
       </c>
       <c r="M12" t="n">
-        <v>0.001437876241392241</v>
-      </c>
-      <c r="N12" t="n">
-        <v>-5.850500413813066e-05</v>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>d</t>
-        </is>
-      </c>
-      <c r="P12" t="n">
+        <v>-0.001124739401628259</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>p</t>
+        </is>
+      </c>
+      <c r="O12" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1118,43 +1080,40 @@
         <v>100</v>
       </c>
       <c r="E13" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G13" t="n">
         <v>0.2</v>
       </c>
-      <c r="F13" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G13" t="n">
-        <v>4</v>
-      </c>
       <c r="H13" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I13" t="n">
-        <v>50</v>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>cos(phi_Dp)cos(phi_kp)</t>
-        </is>
+        <v>40</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>10</v>
       </c>
       <c r="K13" t="n">
-        <v>10</v>
+        <v>-0.02791682671204299</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.0005277022661412283</v>
+        <v>0.00729337282641581</v>
       </c>
       <c r="M13" t="n">
-        <v>0.002048265683601953</v>
-      </c>
-      <c r="N13" t="n">
-        <v>-2.638511330706142e-05</v>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>d</t>
-        </is>
-      </c>
-      <c r="P13" t="n">
+        <v>-0.001395841335602149</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>p</t>
+        </is>
+      </c>
+      <c r="O13" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1172,43 +1131,40 @@
         <v>100</v>
       </c>
       <c r="E14" t="n">
+        <v>8</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G14" t="n">
         <v>0.2</v>
       </c>
-      <c r="F14" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G14" t="n">
-        <v>4.5</v>
-      </c>
       <c r="H14" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I14" t="n">
-        <v>50</v>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>cos(phi_Dp)cos(phi_kp)</t>
-        </is>
+        <v>40</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>10</v>
       </c>
       <c r="K14" t="n">
-        <v>10</v>
+        <v>-0.03349013103185508</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0002729010600625739</v>
+        <v>0.009124834919930326</v>
       </c>
       <c r="M14" t="n">
-        <v>0.002840458150573266</v>
-      </c>
-      <c r="N14" t="n">
-        <v>1.364505300312869e-05</v>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>d</t>
-        </is>
-      </c>
-      <c r="P14" t="n">
+        <v>-0.001674506551592754</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>p</t>
+        </is>
+      </c>
+      <c r="O14" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1226,43 +1182,40 @@
         <v>100</v>
       </c>
       <c r="E15" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G15" t="n">
         <v>0.2</v>
       </c>
-      <c r="F15" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G15" t="n">
-        <v>5</v>
-      </c>
       <c r="H15" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I15" t="n">
-        <v>50</v>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>cos(phi_Dp)cos(phi_kp)</t>
-        </is>
+        <v>40</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>10</v>
       </c>
       <c r="K15" t="n">
-        <v>10</v>
+        <v>-0.0389392126207076</v>
       </c>
       <c r="L15" t="n">
-        <v>0.001186628626672392</v>
+        <v>0.01113205019541564</v>
       </c>
       <c r="M15" t="n">
-        <v>0.003745373962914396</v>
-      </c>
-      <c r="N15" t="n">
-        <v>5.933143133361962e-05</v>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>d</t>
-        </is>
-      </c>
-      <c r="P15" t="n">
+        <v>-0.00194696063103538</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>p</t>
+        </is>
+      </c>
+      <c r="O15" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1280,43 +1233,40 @@
         <v>100</v>
       </c>
       <c r="E16" t="n">
+        <v>9</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G16" t="n">
         <v>0.2</v>
       </c>
-      <c r="F16" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G16" t="n">
-        <v>2</v>
-      </c>
       <c r="H16" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I16" t="n">
-        <v>50</v>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>sin(phi_Dp)sin(phi_kp)</t>
-        </is>
+        <v>40</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>10</v>
       </c>
       <c r="K16" t="n">
-        <v>10</v>
+        <v>-0.04461840575629553</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0002004394139297718</v>
+        <v>0.01347645970444653</v>
       </c>
       <c r="M16" t="n">
-        <v>0.000530860538661124</v>
-      </c>
-      <c r="N16" t="n">
-        <v>1.002197069648859e-05</v>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>d</t>
-        </is>
-      </c>
-      <c r="P16" t="n">
+        <v>-0.002230920287814776</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>p</t>
+        </is>
+      </c>
+      <c r="O16" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1334,43 +1284,40 @@
         <v>100</v>
       </c>
       <c r="E17" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G17" t="n">
         <v>0.2</v>
       </c>
-      <c r="F17" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G17" t="n">
-        <v>2.5</v>
-      </c>
       <c r="H17" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I17" t="n">
-        <v>50</v>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>sin(phi_Dp)sin(phi_kp)</t>
-        </is>
+        <v>40</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>10</v>
       </c>
       <c r="K17" t="n">
-        <v>10</v>
+        <v>-0.0511866498099015</v>
       </c>
       <c r="L17" t="n">
-        <v>2.507216030101972e-05</v>
+        <v>0.01636032330475121</v>
       </c>
       <c r="M17" t="n">
-        <v>0.0007155908433810673</v>
-      </c>
-      <c r="N17" t="n">
-        <v>1.253608015050986e-06</v>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>d</t>
-        </is>
-      </c>
-      <c r="P17" t="n">
+        <v>-0.002559332490495075</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>p</t>
+        </is>
+      </c>
+      <c r="O17" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1388,43 +1335,40 @@
         <v>100</v>
       </c>
       <c r="E18" t="n">
+        <v>10</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G18" t="n">
         <v>0.2</v>
       </c>
-      <c r="F18" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G18" t="n">
-        <v>3</v>
-      </c>
       <c r="H18" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I18" t="n">
-        <v>50</v>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>sin(phi_Dp)sin(phi_kp)</t>
-        </is>
+        <v>40</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>10</v>
       </c>
       <c r="K18" t="n">
-        <v>10</v>
+        <v>-0.05872882789891148</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.0001813747341237582</v>
+        <v>0.01976161302956164</v>
       </c>
       <c r="M18" t="n">
-        <v>0.001008716826647291</v>
-      </c>
-      <c r="N18" t="n">
-        <v>-9.068736706187911e-06</v>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>d</t>
-        </is>
-      </c>
-      <c r="P18" t="n">
+        <v>-0.002936441394945574</v>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>p</t>
+        </is>
+      </c>
+      <c r="O18" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1442,43 +1386,40 @@
         <v>100</v>
       </c>
       <c r="E19" t="n">
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="F19" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G19" t="n">
         <v>0.5</v>
       </c>
-      <c r="G19" t="n">
-        <v>3.5</v>
-      </c>
       <c r="H19" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I19" t="n">
-        <v>50</v>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>sin(phi_Dp)sin(phi_kp)</t>
-        </is>
+        <v>40</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>10</v>
       </c>
       <c r="K19" t="n">
-        <v>10</v>
+        <v>-0.0002333277715613276</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.000403235870869655</v>
+        <v>0.0006159275168960169</v>
       </c>
       <c r="M19" t="n">
-        <v>0.001437876241392241</v>
-      </c>
-      <c r="N19" t="n">
-        <v>-2.016179354348275e-05</v>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>d</t>
-        </is>
-      </c>
-      <c r="P19" t="n">
+        <v>-1.166638857806638e-05</v>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>p</t>
+        </is>
+      </c>
+      <c r="O19" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1496,43 +1437,40 @@
         <v>100</v>
       </c>
       <c r="E20" t="n">
-        <v>0.2</v>
+        <v>2.5</v>
       </c>
       <c r="F20" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G20" t="n">
         <v>0.5</v>
       </c>
-      <c r="G20" t="n">
-        <v>4</v>
-      </c>
       <c r="H20" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I20" t="n">
-        <v>50</v>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>sin(phi_Dp)sin(phi_kp)</t>
-        </is>
+        <v>40</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>10</v>
       </c>
       <c r="K20" t="n">
-        <v>10</v>
+        <v>-0.000315708003381355</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.0006223160283425346</v>
+        <v>0.0006385141487416307</v>
       </c>
       <c r="M20" t="n">
-        <v>0.002048265683601953</v>
-      </c>
-      <c r="N20" t="n">
-        <v>-3.111580141712674e-05</v>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>d</t>
-        </is>
-      </c>
-      <c r="P20" t="n">
+        <v>-1.578540016906775e-05</v>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>p</t>
+        </is>
+      </c>
+      <c r="O20" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1550,43 +1488,40 @@
         <v>100</v>
       </c>
       <c r="E21" t="n">
-        <v>0.2</v>
+        <v>3</v>
       </c>
       <c r="F21" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G21" t="n">
         <v>0.5</v>
       </c>
-      <c r="G21" t="n">
-        <v>4.5</v>
-      </c>
       <c r="H21" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I21" t="n">
-        <v>50</v>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>sin(phi_Dp)sin(phi_kp)</t>
-        </is>
+        <v>40</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>10</v>
       </c>
       <c r="K21" t="n">
-        <v>10</v>
+        <v>-0.0004206889757709382</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.0008130809721881393</v>
+        <v>0.0007046657265733947</v>
       </c>
       <c r="M21" t="n">
-        <v>0.002840458150573266</v>
-      </c>
-      <c r="N21" t="n">
-        <v>-4.065404860940697e-05</v>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>d</t>
-        </is>
-      </c>
-      <c r="P21" t="n">
+        <v>-2.103444878854691e-05</v>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>p</t>
+        </is>
+      </c>
+      <c r="O21" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1604,43 +1539,703 @@
         <v>100</v>
       </c>
       <c r="E22" t="n">
-        <v>0.2</v>
+        <v>3.5</v>
       </c>
       <c r="F22" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G22" t="n">
         <v>0.5</v>
       </c>
-      <c r="G22" t="n">
+      <c r="H22" t="n">
+        <v>40</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>10</v>
+      </c>
+      <c r="K22" t="n">
+        <v>-0.0005807675055765793</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0.0008210096186086957</v>
+      </c>
+      <c r="M22" t="n">
+        <v>-2.903837527882897e-05</v>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>p</t>
+        </is>
+      </c>
+      <c r="O22" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="B23" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>100</v>
+      </c>
+      <c r="E23" t="n">
+        <v>4</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H23" t="n">
+        <v>40</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>10</v>
+      </c>
+      <c r="K23" t="n">
+        <v>-0.0008392810359458006</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0.001000836478893444</v>
+      </c>
+      <c r="M23" t="n">
+        <v>-4.196405179729003e-05</v>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>p</t>
+        </is>
+      </c>
+      <c r="O23" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="B24" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="C24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" t="n">
+        <v>100</v>
+      </c>
+      <c r="E24" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H24" t="n">
+        <v>40</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>10</v>
+      </c>
+      <c r="K24" t="n">
+        <v>-0.001246462422970875</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0.001263392290898606</v>
+      </c>
+      <c r="M24" t="n">
+        <v>-6.232312114854374e-05</v>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>p</t>
+        </is>
+      </c>
+      <c r="O24" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="B25" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="C25" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" t="n">
+        <v>100</v>
+      </c>
+      <c r="E25" t="n">
         <v>5</v>
       </c>
-      <c r="H22" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I22" t="n">
-        <v>50</v>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>sin(phi_Dp)sin(phi_kp)</t>
-        </is>
-      </c>
-      <c r="K22" t="n">
-        <v>10</v>
-      </c>
-      <c r="L22" t="n">
-        <v>-0.0009247133903544681</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0.003745373962914396</v>
-      </c>
-      <c r="N22" t="n">
-        <v>-4.623566951772341e-05</v>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>d</t>
-        </is>
-      </c>
-      <c r="P22" t="n">
+      <c r="F25" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H25" t="n">
+        <v>40</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="J25" t="n">
+        <v>10</v>
+      </c>
+      <c r="K25" t="n">
+        <v>-0.001855045345586928</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0.001633471514105287</v>
+      </c>
+      <c r="M25" t="n">
+        <v>-9.275226727934638e-05</v>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>p</t>
+        </is>
+      </c>
+      <c r="O25" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="B26" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="C26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" t="n">
+        <v>100</v>
+      </c>
+      <c r="E26" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H26" t="n">
+        <v>40</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="J26" t="n">
+        <v>10</v>
+      </c>
+      <c r="K26" t="n">
+        <v>-0.002717574197792458</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0.002141759440655432</v>
+      </c>
+      <c r="M26" t="n">
+        <v>-0.0001358787098896229</v>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>p</t>
+        </is>
+      </c>
+      <c r="O26" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="B27" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="C27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" t="n">
+        <v>100</v>
+      </c>
+      <c r="E27" t="n">
+        <v>6</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H27" t="n">
+        <v>40</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="J27" t="n">
+        <v>10</v>
+      </c>
+      <c r="K27" t="n">
+        <v>-0.00389110408232735</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0.002826163102275314</v>
+      </c>
+      <c r="M27" t="n">
+        <v>-0.0001945552041163675</v>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>p</t>
+        </is>
+      </c>
+      <c r="O27" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="B28" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="C28" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" t="n">
+        <v>100</v>
+      </c>
+      <c r="E28" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H28" t="n">
+        <v>40</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="J28" t="n">
+        <v>10</v>
+      </c>
+      <c r="K28" t="n">
+        <v>-0.005451654693385698</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0.003729723976315734</v>
+      </c>
+      <c r="M28" t="n">
+        <v>-0.0002725827346692849</v>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>p</t>
+        </is>
+      </c>
+      <c r="O28" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="B29" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="C29" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" t="n">
+        <v>100</v>
+      </c>
+      <c r="E29" t="n">
+        <v>7</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H29" t="n">
+        <v>40</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="J29" t="n">
+        <v>10</v>
+      </c>
+      <c r="K29" t="n">
+        <v>-0.007497365425388586</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0.004884421564111851</v>
+      </c>
+      <c r="M29" t="n">
+        <v>-0.0003748682712694293</v>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>p</t>
+        </is>
+      </c>
+      <c r="O29" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="B30" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="C30" t="n">
+        <v>1</v>
+      </c>
+      <c r="D30" t="n">
+        <v>100</v>
+      </c>
+      <c r="E30" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H30" t="n">
+        <v>40</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="J30" t="n">
+        <v>10</v>
+      </c>
+      <c r="K30" t="n">
+        <v>-0.01008759680417437</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0.00627938402890754</v>
+      </c>
+      <c r="M30" t="n">
+        <v>-0.0005043798402087186</v>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>p</t>
+        </is>
+      </c>
+      <c r="O30" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="B31" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="C31" t="n">
+        <v>1</v>
+      </c>
+      <c r="D31" t="n">
+        <v>100</v>
+      </c>
+      <c r="E31" t="n">
+        <v>8</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H31" t="n">
+        <v>40</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="J31" t="n">
+        <v>10</v>
+      </c>
+      <c r="K31" t="n">
+        <v>-0.01312698979319087</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0.00785585886413649</v>
+      </c>
+      <c r="M31" t="n">
+        <v>-0.0006563494896595434</v>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>p</t>
+        </is>
+      </c>
+      <c r="O31" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="B32" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="C32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D32" t="n">
+        <v>100</v>
+      </c>
+      <c r="E32" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H32" t="n">
+        <v>40</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="J32" t="n">
+        <v>10</v>
+      </c>
+      <c r="K32" t="n">
+        <v>-0.01640495535908218</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0.009585987549030575</v>
+      </c>
+      <c r="M32" t="n">
+        <v>-0.000820247767954109</v>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>p</t>
+        </is>
+      </c>
+      <c r="O32" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="B33" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="C33" t="n">
+        <v>1</v>
+      </c>
+      <c r="D33" t="n">
+        <v>100</v>
+      </c>
+      <c r="E33" t="n">
+        <v>9</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H33" t="n">
+        <v>40</v>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="J33" t="n">
+        <v>10</v>
+      </c>
+      <c r="K33" t="n">
+        <v>-0.01988533508967266</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0.01156416109992246</v>
+      </c>
+      <c r="M33" t="n">
+        <v>-0.0009942667544836328</v>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>p</t>
+        </is>
+      </c>
+      <c r="O33" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="B34" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="C34" t="n">
+        <v>1</v>
+      </c>
+      <c r="D34" t="n">
+        <v>100</v>
+      </c>
+      <c r="E34" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H34" t="n">
+        <v>40</v>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="J34" t="n">
+        <v>10</v>
+      </c>
+      <c r="K34" t="n">
+        <v>-0.023885110781641</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0.01396560030146347</v>
+      </c>
+      <c r="M34" t="n">
+        <v>-0.00119425553908205</v>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>p</t>
+        </is>
+      </c>
+      <c r="O34" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="B35" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="C35" t="n">
+        <v>1</v>
+      </c>
+      <c r="D35" t="n">
+        <v>100</v>
+      </c>
+      <c r="E35" t="n">
+        <v>10</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H35" t="n">
+        <v>40</v>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="J35" t="n">
+        <v>10</v>
+      </c>
+      <c r="K35" t="n">
+        <v>-0.02885969435944218</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0.01686531857479182</v>
+      </c>
+      <c r="M35" t="n">
+        <v>-0.001442984717972109</v>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>p</t>
+        </is>
+      </c>
+      <c r="O35" t="n">
         <v>1</v>
       </c>
     </row>
